--- a/sources/ogre_step5.xlsx
+++ b/sources/ogre_step5.xlsx
@@ -722,6 +722,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>d39eb950-752d-4877-9aa7-36a04ab131b5</t>
+        </is>
+      </c>
       <c r="Q6" t="inlineStr">
         <is>
           <t>d39eb950-752d-4877-9aa7-36a04ab131b5</t>
@@ -769,6 +774,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>64b3364c-2ddc-4c41-a1df-c8c0c11f1274</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>64b3364c-2ddc-4c41-a1df-c8c0c11f1274</t>
@@ -814,6 +824,11 @@
       <c r="M8" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>f9b36b8d-0849-48e2-82e6-616a4a498ad1</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
